--- a/Stock_OneClick/history/scan_result_20260601_132042.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_132042.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -670,24 +670,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -739,24 +721,6 @@
       <c r="J4" t="n">
         <v>136.62</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -808,27 +772,15 @@
       <c r="J5" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -877,24 +829,6 @@
       <c r="J6" t="n">
         <v>72.75</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -946,24 +880,12 @@
       <c r="J7" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1015,24 +937,12 @@
       <c r="J8" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=-4.24%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1084,24 +994,6 @@
       <c r="J9" t="n">
         <v>323.39</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-0.16%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1153,24 +1045,12 @@
       <c r="J10" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1222,24 +1102,6 @@
       <c r="J11" t="n">
         <v>14.7</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1291,24 +1153,6 @@
       <c r="J12" t="n">
         <v>320.41</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1360,24 +1204,6 @@
       <c r="J13" t="n">
         <v>185.83</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1429,24 +1255,6 @@
       <c r="J14" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1498,24 +1306,6 @@
       <c r="J15" t="n">
         <v>27.15</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1567,24 +1357,6 @@
       <c r="J16" t="n">
         <v>50.55</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1636,24 +1408,6 @@
       <c r="J17" t="n">
         <v>905</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1705,24 +1459,6 @@
       <c r="J18" t="n">
         <v>11.02</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1774,24 +1510,6 @@
       <c r="J19" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1843,24 +1561,6 @@
       <c r="J20" t="n">
         <v>58.92</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1912,24 +1612,6 @@
       <c r="J21" t="n">
         <v>13.89</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1981,24 +1663,6 @@
       <c r="J22" t="n">
         <v>15.58</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2050,24 +1714,12 @@
       <c r="J23" s="5" t="n">
         <v>155.71</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2119,24 +1771,12 @@
       <c r="J24" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2188,24 +1828,6 @@
       <c r="J25" t="n">
         <v>163.09</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2257,24 +1879,6 @@
       <c r="J26" t="n">
         <v>54.5</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%</t>
@@ -2326,24 +1930,6 @@
       <c r="J27" t="n">
         <v>16.62</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2395,24 +1981,12 @@
       <c r="J28" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2464,24 +2038,6 @@
       <c r="J29" t="n">
         <v>47.59</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.10%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2533,24 +2089,6 @@
       <c r="J30" t="n">
         <v>400.08</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2602,24 +2140,6 @@
       <c r="J31" t="n">
         <v>950.54</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.49%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2671,24 +2191,12 @@
       <c r="J32" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2740,24 +2248,6 @@
       <c r="J33" t="n">
         <v>23.33</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2809,24 +2299,6 @@
       <c r="J34" t="n">
         <v>251.49</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%</t>
@@ -2878,24 +2350,6 @@
       <c r="J35" t="n">
         <v>145.02</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%</t>
@@ -2947,24 +2401,6 @@
       <c r="J36" t="n">
         <v>255.71</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -3016,24 +2452,12 @@
       <c r="J37" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3085,24 +2509,12 @@
       <c r="J38" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%</t>
@@ -3154,24 +2566,12 @@
       <c r="J39" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3223,24 +2623,6 @@
       <c r="J40" t="n">
         <v>459.97</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%</t>
@@ -3292,24 +2674,6 @@
       <c r="J41" t="n">
         <v>91.22</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%</t>
@@ -3361,24 +2725,12 @@
       <c r="J42" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3430,24 +2782,6 @@
       <c r="J43" t="n">
         <v>124.82</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3495,24 +2829,12 @@
       <c r="J44" s="5" t="n">
         <v>86.77</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-1.95%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3560,24 +2882,12 @@
       <c r="J45" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-6.73%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3629,24 +2939,12 @@
       <c r="J46" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3698,24 +2996,12 @@
       <c r="J47" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%</t>
@@ -3767,24 +3053,6 @@
       <c r="J48" t="n">
         <v>108.96</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%</t>
@@ -3836,24 +3104,12 @@
       <c r="J49" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%</t>
@@ -3905,24 +3161,6 @@
       <c r="J50" t="n">
         <v>83.78</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%</t>
@@ -3974,24 +3212,12 @@
       <c r="J51" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%</t>
@@ -4039,24 +3265,12 @@
       <c r="J52" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=0.18%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4104,24 +3318,12 @@
       <c r="J53" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-6.19%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4173,24 +3375,12 @@
       <c r="J54" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%</t>
@@ -4242,24 +3432,6 @@
       <c r="J55" t="n">
         <v>248.15</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.95%</t>
@@ -4311,24 +3483,6 @@
       <c r="J56" t="n">
         <v>273.51</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%</t>
@@ -4380,24 +3534,12 @@
       <c r="J57" s="5" t="n">
         <v>782.17</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4449,24 +3591,6 @@
       <c r="J58" t="n">
         <v>64.61</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%</t>
@@ -4514,24 +3638,12 @@
       <c r="J59" s="5" t="n">
         <v>1050.77</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-1.75%</t>
@@ -4583,24 +3695,12 @@
       <c r="J60" s="5" t="n">
         <v>147.14</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%</t>
@@ -4652,24 +3752,12 @@
       <c r="J61" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%</t>
@@ -4721,24 +3809,12 @@
       <c r="J62" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%</t>
@@ -4790,24 +3866,6 @@
       <c r="J63" t="n">
         <v>264.51</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%</t>
@@ -4859,24 +3917,12 @@
       <c r="J64" s="5" t="n">
         <v>139.79</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%</t>
@@ -4928,24 +3974,12 @@
       <c r="J65" s="5" t="n">
         <v>300.48</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4997,24 +4031,12 @@
       <c r="J66" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%</t>
@@ -5066,24 +4088,12 @@
       <c r="J67" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%</t>
@@ -5135,24 +4145,12 @@
       <c r="J68" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%</t>
@@ -5204,24 +4202,6 @@
       <c r="J69" t="n">
         <v>115.58</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5269,24 +4249,12 @@
       <c r="J70" s="5" t="n">
         <v>99.19499999999999</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=99.19; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5334,24 +4302,12 @@
       <c r="J71" s="5" t="n">
         <v>16.01</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=16.01; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5588,24 +4544,12 @@
       <c r="J83" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -5657,24 +4601,6 @@
       <c r="J84" t="n">
         <v>105.65</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5726,24 +4652,6 @@
       <c r="J85" t="n">
         <v>64.61</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5795,24 +4703,12 @@
       <c r="J86" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5864,24 +4760,12 @@
       <c r="J87" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5933,24 +4817,12 @@
       <c r="J88" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -6002,24 +4874,12 @@
       <c r="J89" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -6071,24 +4931,12 @@
       <c r="J90" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%</t>
@@ -6109,7 +4957,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6136,24 +4983,6 @@
       <c r="J91" t="n">
         <v>91.03</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=0.43%</t>
@@ -6205,24 +5034,12 @@
       <c r="J92" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%</t>
@@ -6274,24 +5091,12 @@
       <c r="J93" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%</t>
@@ -6312,7 +5117,6 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6339,24 +5143,6 @@
       <c r="J94" t="n">
         <v>38.79</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-06-01; 相对D0=3.14%</t>
@@ -6408,24 +5194,6 @@
       <c r="J95" t="n">
         <v>403.88</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%</t>
@@ -6477,24 +5245,12 @@
       <c r="J96" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%</t>
@@ -6546,24 +5302,12 @@
       <c r="J97" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%</t>
@@ -6615,24 +5359,12 @@
       <c r="J98" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%</t>
@@ -6684,24 +5416,6 @@
       <c r="J99" t="n">
         <v>155.71</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%</t>
@@ -6753,24 +5467,12 @@
       <c r="J100" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%</t>
@@ -6822,24 +5524,6 @@
       <c r="J101" t="n">
         <v>265.7</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%</t>
@@ -6891,24 +5575,12 @@
       <c r="J102" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%</t>
@@ -6960,24 +5632,6 @@
       <c r="J103" t="n">
         <v>492.29</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%</t>
@@ -7029,24 +5683,12 @@
       <c r="J104" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%</t>
@@ -7098,24 +5740,12 @@
       <c r="J105" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%</t>
@@ -7167,24 +5797,6 @@
       <c r="J106" t="n">
         <v>273.51</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%</t>
@@ -7236,24 +5848,12 @@
       <c r="J107" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%</t>
@@ -7305,24 +5905,6 @@
       <c r="J108" t="n">
         <v>27.15</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%</t>
@@ -7374,24 +5956,6 @@
       <c r="J109" t="n">
         <v>109.33</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%</t>
@@ -7443,24 +6007,12 @@
       <c r="J110" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%</t>
@@ -7512,24 +6064,12 @@
       <c r="J111" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P111" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="5" t="n"/>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="5" t="n"/>
       <c r="Q111" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%</t>
@@ -7626,7 +6166,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7638,7 +6177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7736,9 +6275,7 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -7783,9 +6320,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7834,9 +6369,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="17" t="n"/>
       <c r="C5" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7885,9 +6418,7 @@
           <t>NOW</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -7932,9 +6463,7 @@
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="10" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -8131,9 +6660,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -8178,9 +6705,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8270,10 +6795,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8285,7 +6806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8371,9 +6892,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -8412,9 +6931,7 @@
           <t>CRWD</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8453,9 +6970,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -8494,9 +7009,7 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8535,9 +7048,7 @@
           <t>FTNT</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="10" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8576,9 +7087,7 @@
           <t>IGV</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="10" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -8617,9 +7126,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="17" t="n"/>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -8658,9 +7165,7 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="13" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -8691,7 +7196,6 @@
       <c r="J10" s="15" t="n">
         <v>0.16864</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8699,9 +7203,7 @@
           <t>OKTA</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8740,9 +7242,7 @@
           <t>PANW</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8781,9 +7281,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -8977,9 +7475,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B25" s="10" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9018,9 +7514,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="10" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -9059,9 +7553,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9100,9 +7592,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="10" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -9199,9 +7689,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9213,7 +7700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9287,9 +7774,7 @@
           <t>ADBE</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -9302,7 +7787,7 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="16" t="n">
@@ -9322,9 +7807,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -9357,9 +7840,7 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="17" t="n"/>
       <c r="C5" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -9515,9 +7996,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="10" t="n"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9550,9 +8029,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="10" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9585,9 +8062,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="10" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9620,9 +8095,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9659,9 +8132,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9694,9 +8165,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B20" s="10" t="n"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9729,9 +8198,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B21" s="10" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -9764,9 +8231,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B22" s="10" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -9799,9 +8264,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B23" s="10" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9918,7 +8381,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9930,7 +8392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10100,7 +8562,6 @@
       <c r="F6" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -10187,7 +8648,6 @@
       <c r="F9" t="n">
         <v>15.58</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -10332,7 +8792,6 @@
       <c r="F14" t="n">
         <v>14.7</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -10369,9 +8828,7 @@
           <t>COP</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="10" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -10398,9 +8855,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -10427,9 +8882,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -10591,9 +9044,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="10" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -10620,9 +9071,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="10" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -10649,9 +9098,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -10678,9 +9125,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10707,9 +9152,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="10" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -10736,9 +9179,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="10" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10849,7 +9290,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12013,8 +10453,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.98; 4H分金=54.88</t>
@@ -12444,8 +10882,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=49.02; 4H分金=55.10</t>
@@ -13090,7 +11526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13484,8 +11920,6 @@
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=39.36; 4H分金=37.70</t>
@@ -14002,8 +12436,6 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=44.86; 4H分金=51.19</t>
@@ -15477,8 +13909,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=40.25; 4H分金=32.84</t>
@@ -15560,8 +13990,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.15; 4H分金=54.64</t>
@@ -16068,7 +14496,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -16117,7 +14544,6 @@
           <t>98 超巨</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -16172,7 +14598,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -16278,7 +14703,6 @@
       <c r="D6" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46170</v>
       </c>
@@ -16937,7 +15361,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -17049,7 +15472,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -17138,7 +15560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17260,9 +15682,7 @@
           <t>AAOI</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17323,9 +15743,7 @@
           <t>BWXT</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -17386,9 +15804,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17449,9 +15865,7 @@
           <t>COHU</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17508,9 +15922,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="13" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -17571,9 +15983,7 @@
           <t>CRM</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -17634,9 +16044,7 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="10" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17697,9 +16105,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="13" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -17760,9 +16166,7 @@
           <t>ETN</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17823,9 +16227,7 @@
           <t>GEV</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17886,9 +16288,7 @@
           <t>LEU</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="10" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -17949,9 +16349,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B14" s="10" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -18012,9 +16410,7 @@
           <t>MOS</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>18 化肥</t>
@@ -18075,9 +16471,7 @@
           <t>NUE</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="13" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -18126,7 +16520,6 @@
       <c r="P16" s="15" t="n">
         <v>0.084009</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -18134,9 +16527,7 @@
           <t>NXT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="16" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -18193,9 +16584,7 @@
           <t>ONTO</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -18256,9 +16645,7 @@
           <t>TEAM</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="17" t="n"/>
       <c r="C19" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -18319,9 +16706,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B20" s="13" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -18370,7 +16755,6 @@
       <c r="P20" s="14" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -18378,9 +16762,7 @@
           <t>UEC</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B21" s="10" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -18626,9 +17008,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -18717,11 +17097,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18733,7 +17108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18894,24 +17269,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18963,24 +17326,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19032,24 +17383,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19101,24 +17440,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19170,24 +17497,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19239,24 +17548,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19308,24 +17605,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19377,24 +17662,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19446,24 +17713,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19515,24 +17770,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19584,24 +17827,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19653,24 +17884,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19722,24 +17941,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19791,24 +17992,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19860,24 +18043,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19929,24 +18094,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19998,24 +18151,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20067,24 +18208,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20136,24 +18259,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20390,24 +18501,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20452,11 +18551,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20468,7 +18562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -20578,9 +18672,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20635,9 +18727,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="17" t="n"/>
       <c r="C4" s="16" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -20688,9 +18778,7 @@
           <t>BHP</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -20741,9 +18829,7 @@
           <t>CCJ</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -20798,9 +18884,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="13" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -20855,9 +18939,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -20912,9 +18994,7 @@
           <t>GDXU</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="10" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -20969,9 +19049,7 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="17" t="n"/>
       <c r="C10" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -21026,9 +19104,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -21079,9 +19155,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21094,7 +19168,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -21136,9 +19210,7 @@
           <t>RIO</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="16" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -21189,9 +19261,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B14" s="10" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21204,7 +19274,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -21242,9 +19312,7 @@
           <t>SOLS</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="16" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -21295,9 +19363,7 @@
           <t>UUUU</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="10" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21352,9 +19418,7 @@
           <t>VRT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="16" t="inlineStr">
         <is>
           <t>06 服务器 / 数据中心硬件</t>
@@ -21584,9 +19648,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="10" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21637,9 +19699,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="10" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21690,9 +19750,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="10" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21743,9 +19801,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21796,9 +19852,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -21849,9 +19903,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="10" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21902,9 +19954,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="10" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22026,8 +20076,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
